--- a/DataTables/Doctor_条目解锁顺序.xlsx
+++ b/DataTables/Doctor_条目解锁顺序.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15DCD724-B7EA-4E8A-9945-7A19089D299C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8469BF1-F2F8-4D64-999F-1AB5191135F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总览" sheetId="1" r:id="rId1"/>
@@ -2569,11 +2569,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2584,20 +2590,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2913,32 +2913,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
     </row>
     <row r="3" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
     </row>
     <row r="4" spans="1:6" ht="21.95" customHeight="1">
       <c r="A4" s="1"/>
@@ -3083,54 +3083,54 @@
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="28"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="30"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
     </row>
     <row r="18" spans="1:6" ht="21.95" customHeight="1">
       <c r="A18" s="1"/>
@@ -3149,14 +3149,14 @@
       <c r="F19" s="1"/>
     </row>
     <row r="20" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="28"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="30"/>
     </row>
     <row r="21" spans="1:6" ht="26.1" customHeight="1">
       <c r="A21" s="5" t="s">
@@ -3174,40 +3174,45 @@
       <c r="A22" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
     </row>
     <row r="23" spans="1:6" ht="26.1" customHeight="1">
       <c r="A23" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B23" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
     </row>
     <row r="24" spans="1:6" ht="26.1" customHeight="1">
       <c r="A24" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A15:F15"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="A16:F16"/>
@@ -3215,11 +3220,6 @@
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B22:F22"/>
-    <mergeCell ref="A1:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
